--- a/artfynd/A 26313-2024 artfynd.xlsx
+++ b/artfynd/A 26313-2024 artfynd.xlsx
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118370942</v>
+        <v>118371042</v>
       </c>
       <c r="B15" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,38 +2220,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497608</v>
+        <v>497707</v>
       </c>
       <c r="R15" t="n">
-        <v>6910759</v>
+        <v>6910701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2320,10 +2329,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118371042</v>
+        <v>118370942</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2332,47 +2341,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497707</v>
+        <v>497608</v>
       </c>
       <c r="R16" t="n">
-        <v>6910701</v>
+        <v>6910759</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 26313-2024 artfynd.xlsx
+++ b/artfynd/A 26313-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118370526</v>
+        <v>118370412</v>
       </c>
       <c r="B3" t="n">
-        <v>96801</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,38 +816,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497767</v>
+        <v>497790</v>
       </c>
       <c r="R3" t="n">
-        <v>6910789</v>
+        <v>6910754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118370858</v>
+        <v>118371042</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,38 +937,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497611</v>
+        <v>497707</v>
       </c>
       <c r="R4" t="n">
-        <v>6910805</v>
+        <v>6910701</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118370834</v>
+        <v>118370597</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,38 +1058,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497611</v>
+        <v>497757</v>
       </c>
       <c r="R5" t="n">
-        <v>6910806</v>
+        <v>6910791</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118370260</v>
+        <v>118370966</v>
       </c>
       <c r="B6" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1179,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497790</v>
+        <v>497622</v>
       </c>
       <c r="R6" t="n">
-        <v>6910717</v>
+        <v>6910750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,10 +1288,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118370818</v>
+        <v>118370260</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,47 +1300,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497611</v>
+        <v>497790</v>
       </c>
       <c r="R7" t="n">
-        <v>6910806</v>
+        <v>6910717</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118370706</v>
+        <v>118370818</v>
       </c>
       <c r="B8" t="n">
-        <v>91969</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,38 +1412,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497688</v>
+        <v>497611</v>
       </c>
       <c r="R8" t="n">
-        <v>6910776</v>
+        <v>6910806</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118370370</v>
+        <v>118370942</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,47 +1533,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497756</v>
+        <v>497608</v>
       </c>
       <c r="R9" t="n">
-        <v>6910746</v>
+        <v>6910759</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118370966</v>
+        <v>118370706</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>91969</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,47 +1645,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497622</v>
+        <v>497688</v>
       </c>
       <c r="R10" t="n">
-        <v>6910750</v>
+        <v>6910776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118371070</v>
+        <v>118370792</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,47 +1757,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497712</v>
+        <v>497654</v>
       </c>
       <c r="R11" t="n">
-        <v>6910702</v>
+        <v>6910788</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118370597</v>
+        <v>118370526</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>96801</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,47 +1869,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497757</v>
+        <v>497767</v>
       </c>
       <c r="R12" t="n">
-        <v>6910791</v>
+        <v>6910789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118370792</v>
+        <v>118370858</v>
       </c>
       <c r="B13" t="n">
         <v>79565</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497654</v>
+        <v>497611</v>
       </c>
       <c r="R13" t="n">
-        <v>6910788</v>
+        <v>6910805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118370567</v>
+        <v>118370370</v>
       </c>
       <c r="B14" t="n">
-        <v>56502</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,41 +2093,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2136,10 +2130,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497771</v>
+        <v>497756</v>
       </c>
       <c r="R14" t="n">
-        <v>6910758</v>
+        <v>6910746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,7 +2202,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118371042</v>
+        <v>118371070</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2243,7 +2237,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2257,10 +2251,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497707</v>
+        <v>497712</v>
       </c>
       <c r="R15" t="n">
-        <v>6910701</v>
+        <v>6910702</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118370942</v>
+        <v>118370834</v>
       </c>
       <c r="B16" t="n">
-        <v>78221</v>
+        <v>79565</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2345,21 +2339,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2369,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497608</v>
+        <v>497611</v>
       </c>
       <c r="R16" t="n">
-        <v>6910759</v>
+        <v>6910806</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2441,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118370412</v>
+        <v>118370567</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2453,35 +2447,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497790</v>
+        <v>497771</v>
       </c>
       <c r="R17" t="n">
-        <v>6910754</v>
+        <v>6910758</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 26313-2024 artfynd.xlsx
+++ b/artfynd/A 26313-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118370412</v>
+        <v>118371070</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497790</v>
+        <v>497712</v>
       </c>
       <c r="R3" t="n">
-        <v>6910754</v>
+        <v>6910702</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118371042</v>
+        <v>118370942</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,47 +937,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497707</v>
+        <v>497608</v>
       </c>
       <c r="R4" t="n">
-        <v>6910701</v>
+        <v>6910759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118370597</v>
+        <v>118370526</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>96801</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,47 +1049,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497757</v>
+        <v>497767</v>
       </c>
       <c r="R5" t="n">
-        <v>6910791</v>
+        <v>6910789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1167,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118370966</v>
+        <v>118370834</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,47 +1161,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497622</v>
+        <v>497611</v>
       </c>
       <c r="R6" t="n">
-        <v>6910750</v>
+        <v>6910806</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118370260</v>
+        <v>118370966</v>
       </c>
       <c r="B7" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,38 +1273,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497790</v>
+        <v>497622</v>
       </c>
       <c r="R7" t="n">
-        <v>6910717</v>
+        <v>6910750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1400,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118370818</v>
+        <v>118370412</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1435,7 +1417,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1449,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497611</v>
+        <v>497790</v>
       </c>
       <c r="R8" t="n">
-        <v>6910806</v>
+        <v>6910754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1521,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118370942</v>
+        <v>118370818</v>
       </c>
       <c r="B9" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,38 +1515,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497608</v>
+        <v>497611</v>
       </c>
       <c r="R9" t="n">
-        <v>6910759</v>
+        <v>6910806</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118370706</v>
+        <v>118370597</v>
       </c>
       <c r="B10" t="n">
-        <v>91969</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,38 +1636,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497688</v>
+        <v>497757</v>
       </c>
       <c r="R10" t="n">
-        <v>6910776</v>
+        <v>6910791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118370792</v>
+        <v>118371042</v>
       </c>
       <c r="B11" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,38 +1757,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497654</v>
+        <v>497707</v>
       </c>
       <c r="R11" t="n">
-        <v>6910788</v>
+        <v>6910701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1857,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118370526</v>
+        <v>118370260</v>
       </c>
       <c r="B12" t="n">
-        <v>96801</v>
+        <v>78221</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,25 +1878,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1897,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497767</v>
+        <v>497790</v>
       </c>
       <c r="R12" t="n">
-        <v>6910789</v>
+        <v>6910717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2081,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118370370</v>
+        <v>118370706</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>91969</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,47 +2102,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497756</v>
+        <v>497688</v>
       </c>
       <c r="R14" t="n">
-        <v>6910746</v>
+        <v>6910776</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118371070</v>
+        <v>118370792</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,47 +2214,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497712</v>
+        <v>497654</v>
       </c>
       <c r="R15" t="n">
-        <v>6910702</v>
+        <v>6910788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2323,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118370834</v>
+        <v>118370370</v>
       </c>
       <c r="B16" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,38 +2326,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497611</v>
+        <v>497756</v>
       </c>
       <c r="R16" t="n">
-        <v>6910806</v>
+        <v>6910746</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 26313-2024 artfynd.xlsx
+++ b/artfynd/A 26313-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118371070</v>
+        <v>118370858</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,47 +816,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497712</v>
+        <v>497611</v>
       </c>
       <c r="R3" t="n">
-        <v>6910702</v>
+        <v>6910805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -925,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118370942</v>
+        <v>118370818</v>
       </c>
       <c r="B4" t="n">
-        <v>78221</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,38 +928,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497608</v>
+        <v>497611</v>
       </c>
       <c r="R4" t="n">
-        <v>6910759</v>
+        <v>6910806</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118370526</v>
+        <v>118370706</v>
       </c>
       <c r="B5" t="n">
-        <v>96801</v>
+        <v>91976</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,25 +1049,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497767</v>
+        <v>497688</v>
       </c>
       <c r="R5" t="n">
-        <v>6910789</v>
+        <v>6910776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118370834</v>
+        <v>118371070</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,38 +1161,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497611</v>
+        <v>497712</v>
       </c>
       <c r="R6" t="n">
-        <v>6910806</v>
+        <v>6910702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118370966</v>
+        <v>118370792</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,47 +1282,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497622</v>
+        <v>497654</v>
       </c>
       <c r="R7" t="n">
-        <v>6910750</v>
+        <v>6910788</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118370412</v>
+        <v>118370526</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>96808</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,47 +1394,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497790</v>
+        <v>497767</v>
       </c>
       <c r="R8" t="n">
-        <v>6910754</v>
+        <v>6910789</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118370818</v>
+        <v>118370260</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>78228</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,47 +1506,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497611</v>
+        <v>497790</v>
       </c>
       <c r="R9" t="n">
-        <v>6910806</v>
+        <v>6910717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1624,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118370597</v>
+        <v>118370966</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1659,7 +1641,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1673,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497757</v>
+        <v>497622</v>
       </c>
       <c r="R10" t="n">
-        <v>6910791</v>
+        <v>6910750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1745,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118371042</v>
+        <v>118370597</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,7 +1762,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1794,10 +1776,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497707</v>
+        <v>497757</v>
       </c>
       <c r="R11" t="n">
-        <v>6910701</v>
+        <v>6910791</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1866,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118370260</v>
+        <v>118371042</v>
       </c>
       <c r="B12" t="n">
-        <v>78221</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,38 +1860,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497790</v>
+        <v>497707</v>
       </c>
       <c r="R12" t="n">
-        <v>6910717</v>
+        <v>6910701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118370858</v>
+        <v>118370567</v>
       </c>
       <c r="B13" t="n">
-        <v>79565</v>
+        <v>56502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,38 +1981,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497611</v>
+        <v>497771</v>
       </c>
       <c r="R13" t="n">
-        <v>6910805</v>
+        <v>6910758</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2090,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118370706</v>
+        <v>118370834</v>
       </c>
       <c r="B14" t="n">
-        <v>91969</v>
+        <v>79572</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2106,21 +2112,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497688</v>
+        <v>497611</v>
       </c>
       <c r="R14" t="n">
-        <v>6910776</v>
+        <v>6910806</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118370792</v>
+        <v>118370412</v>
       </c>
       <c r="B15" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,38 +2220,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497654</v>
+        <v>497790</v>
       </c>
       <c r="R15" t="n">
-        <v>6910788</v>
+        <v>6910754</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2317,7 +2332,7 @@
         <v>118370370</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2435,10 +2450,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118370567</v>
+        <v>118370942</v>
       </c>
       <c r="B17" t="n">
-        <v>56502</v>
+        <v>78228</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,53 +2462,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497771</v>
+        <v>497608</v>
       </c>
       <c r="R17" t="n">
-        <v>6910758</v>
+        <v>6910759</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 26313-2024 artfynd.xlsx
+++ b/artfynd/A 26313-2024 artfynd.xlsx
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118371042</v>
+        <v>118370567</v>
       </c>
       <c r="B12" t="n">
-        <v>97853</v>
+        <v>56502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,35 +1860,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1897,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497707</v>
+        <v>497771</v>
       </c>
       <c r="R12" t="n">
-        <v>6910701</v>
+        <v>6910758</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1969,10 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118370567</v>
+        <v>118371042</v>
       </c>
       <c r="B13" t="n">
-        <v>56502</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,41 +1987,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497771</v>
+        <v>497707</v>
       </c>
       <c r="R13" t="n">
-        <v>6910758</v>
+        <v>6910701</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 26313-2024 artfynd.xlsx
+++ b/artfynd/A 26313-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118370858</v>
+        <v>118370597</v>
       </c>
       <c r="B3" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,38 +816,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497611</v>
+        <v>497757</v>
       </c>
       <c r="R3" t="n">
-        <v>6910805</v>
+        <v>6910791</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118370818</v>
+        <v>118370412</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -951,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -965,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497611</v>
+        <v>497790</v>
       </c>
       <c r="R4" t="n">
-        <v>6910806</v>
+        <v>6910754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118370706</v>
+        <v>118370966</v>
       </c>
       <c r="B5" t="n">
-        <v>91976</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,38 +1058,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497688</v>
+        <v>497622</v>
       </c>
       <c r="R5" t="n">
-        <v>6910776</v>
+        <v>6910750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118371070</v>
+        <v>118370792</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,47 +1179,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497712</v>
+        <v>497654</v>
       </c>
       <c r="R6" t="n">
-        <v>6910702</v>
+        <v>6910788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1270,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118370792</v>
+        <v>118370526</v>
       </c>
       <c r="B7" t="n">
-        <v>79572</v>
+        <v>96808</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1291,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497654</v>
+        <v>497767</v>
       </c>
       <c r="R7" t="n">
-        <v>6910788</v>
+        <v>6910789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118370526</v>
+        <v>118371070</v>
       </c>
       <c r="B8" t="n">
-        <v>96808</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,38 +1403,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497767</v>
+        <v>497712</v>
       </c>
       <c r="R8" t="n">
-        <v>6910789</v>
+        <v>6910702</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1494,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118370260</v>
+        <v>118370818</v>
       </c>
       <c r="B9" t="n">
-        <v>78228</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,38 +1524,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497790</v>
+        <v>497611</v>
       </c>
       <c r="R9" t="n">
-        <v>6910717</v>
+        <v>6910806</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,7 +1633,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118370966</v>
+        <v>118371042</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1641,7 +1668,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1655,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497622</v>
+        <v>497707</v>
       </c>
       <c r="R10" t="n">
-        <v>6910750</v>
+        <v>6910701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1727,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118370597</v>
+        <v>118370706</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>91976</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,47 +1766,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497757</v>
+        <v>497688</v>
       </c>
       <c r="R11" t="n">
-        <v>6910791</v>
+        <v>6910776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,10 +1866,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118370567</v>
+        <v>118370370</v>
       </c>
       <c r="B12" t="n">
-        <v>56502</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,41 +1878,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1903,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497771</v>
+        <v>497756</v>
       </c>
       <c r="R12" t="n">
-        <v>6910758</v>
+        <v>6910746</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118371042</v>
+        <v>118370858</v>
       </c>
       <c r="B13" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,47 +1999,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497707</v>
+        <v>497611</v>
       </c>
       <c r="R13" t="n">
-        <v>6910701</v>
+        <v>6910805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2096,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118370834</v>
+        <v>118370567</v>
       </c>
       <c r="B14" t="n">
-        <v>79572</v>
+        <v>56502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,38 +2111,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497611</v>
+        <v>497771</v>
       </c>
       <c r="R14" t="n">
-        <v>6910806</v>
+        <v>6910758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,10 +2226,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118370412</v>
+        <v>118370260</v>
       </c>
       <c r="B15" t="n">
-        <v>97853</v>
+        <v>78228</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,37 +2238,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
@@ -2260,7 +2269,7 @@
         <v>497790</v>
       </c>
       <c r="R15" t="n">
-        <v>6910754</v>
+        <v>6910717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118370370</v>
+        <v>118370834</v>
       </c>
       <c r="B16" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2341,47 +2350,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storkullstjärnen (Storkullstjärnen), Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497756</v>
+        <v>497611</v>
       </c>
       <c r="R16" t="n">
-        <v>6910746</v>
+        <v>6910806</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 26313-2024 artfynd.xlsx
+++ b/artfynd/A 26313-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441810</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370792</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370834</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370858</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370567</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370370</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370412</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1684,6 +1729,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370597</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,6 +1850,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370818</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1916,6 +1971,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370966</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118371042</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2148,6 +2213,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118371070</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2258,6 +2328,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119290089</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2368,6 +2443,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119290119</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2478,6 +2558,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119290129</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2588,6 +2673,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119290134</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2698,6 +2788,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119290145</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2805,6 +2900,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370526</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370260</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3019,8 +3124,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118370942</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>